--- a/data/etf_metadata.xlsx
+++ b/data/etf_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dan13\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90A578D-B1C5-40CD-B37E-149987F7379D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB84CE26-8093-4C72-9214-8E0DC222249A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,15 +17,25 @@
     <sheet name="geography" sheetId="2" r:id="rId2"/>
     <sheet name="sector" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
-  <si>
-    <t>etf_key</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
   <si>
     <t>ticker</t>
   </si>
@@ -132,66 +142,74 @@
     <t>Global all-world equity ETF; accumulating share class.</t>
   </si>
   <si>
-    <t>geography_key</t>
-  </si>
-  <si>
     <t>exposure_weight</t>
   </si>
   <si>
+    <t>Developed ex-US</t>
+  </si>
+  <si>
+    <t>Emerging Markets</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
     <t>US</t>
   </si>
   <si>
     <t>UK</t>
   </si>
   <si>
-    <t>Developed ex-US</t>
-  </si>
-  <si>
-    <t>Emerging Markets</t>
-  </si>
-  <si>
-    <t>sector_key</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Financials</t>
-  </si>
-  <si>
-    <t>Consumer Discretionary</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Consumer Staples</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Materials</t>
-  </si>
-  <si>
-    <t>Utilities</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>etf</t>
+  </si>
+  <si>
+    <t>sector</t>
+  </si>
+  <si>
+    <t>geography</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,6 +222,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -249,20 +274,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -279,7 +322,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tbl_etf_info" displayName="tbl_etf_info" ref="A1:S2">
   <autoFilter ref="A1:S2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="etf_key"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="etf"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ticker"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="isin"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="fund_name"/>
@@ -294,7 +337,7 @@
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="domicile"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="hedged_flag"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="ucits_flag"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="ter"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="ter" dataDxfId="1"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="inception_date"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="is_active"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="notes"/>
@@ -304,24 +347,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tbl_geo" displayName="tbl_geo" ref="A1:C5">
-  <autoFilter ref="A1:C5" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tbl_geo" displayName="tbl_geo" ref="A1:C6">
+  <autoFilter ref="A1:C6" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="etf_key"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="geography_key"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="exposure_weight"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="etf"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="geography"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="exposure_weight" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tbl_sector" displayName="tbl_sector" ref="A1:C11">
-  <autoFilter ref="A1:C11" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tbl_sector" displayName="tbl_sector" ref="A1:C13">
+  <autoFilter ref="A1:C13" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="etf_key"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="sector_key"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="exposure_weight"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="etf"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="sector"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="exposure_weight" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -630,128 +673,128 @@
     <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="49.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="4">
+        <v>0.19</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="P2" s="3">
-        <v>0.22</v>
-      </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -764,206 +807,240 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>37</v>
+      <c r="A1" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0.6</v>
+        <v>48</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="5">
+        <v>49</v>
+      </c>
+      <c r="C3" s="4">
         <v>0.04</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="5">
+        <v>36</v>
+      </c>
+      <c r="C4" s="4">
         <v>0.26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0.1</v>
+        <v>37</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>37</v>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0.23</v>
+        <v>38</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.29470000000000002</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0.15</v>
+        <v>39</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1552</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0.13</v>
+        <v>41</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.13370000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0.1</v>
+        <v>40</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1235</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0.1</v>
+        <v>42</v>
+      </c>
+      <c r="C6" s="4">
+        <v>8.5500000000000007E-2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="5">
-        <v>7.0000000000000007E-2</v>
+        <v>43</v>
+      </c>
+      <c r="C7" s="4">
+        <v>4.5499999999999999E-2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0.05</v>
+        <v>44</v>
+      </c>
+      <c r="C8" s="4">
+        <v>4.2099999999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0.04</v>
+        <v>45</v>
+      </c>
+      <c r="C9" s="4">
+        <v>3.7499999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="5">
-        <v>0.03</v>
+      <c r="C10" s="4">
+        <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0.03</v>
+        <v>46</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2.9899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2.0299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1E-4</v>
       </c>
     </row>
   </sheetData>

--- a/data/etf_metadata.xlsx
+++ b/data/etf_metadata.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dan13\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB84CE26-8093-4C72-9214-8E0DC222249A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7176077F-3EA2-489C-BD92-15A7BF0F6E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="etf" sheetId="1" r:id="rId1"/>
     <sheet name="geography" sheetId="2" r:id="rId2"/>
     <sheet name="sector" sheetId="3" r:id="rId3"/>
+    <sheet name="equivalence_groups" sheetId="4" r:id="rId4"/>
+    <sheet name="equivalence_group_relationships" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="109">
   <si>
     <t>ticker</t>
   </si>
@@ -46,15 +48,6 @@
     <t>fund_name</t>
   </si>
   <si>
-    <t>provider_key</t>
-  </si>
-  <si>
-    <t>index_key</t>
-  </si>
-  <si>
-    <t>equivalence_group_key</t>
-  </si>
-  <si>
     <t>asset_class</t>
   </si>
   <si>
@@ -109,9 +102,6 @@
     <t>FTSE_ALL_WORLD</t>
   </si>
   <si>
-    <t>GLOBAL_ALL_WORLD</t>
-  </si>
-  <si>
     <t>Equity</t>
   </si>
   <si>
@@ -200,6 +190,180 @@
   </si>
   <si>
     <t>geography</t>
+  </si>
+  <si>
+    <t>equivalence_group_code</t>
+  </si>
+  <si>
+    <t>global_all_world</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>provider</t>
+  </si>
+  <si>
+    <t>Broad global aggregate bond exposure.</t>
+  </si>
+  <si>
+    <t>Global investment-grade bonds</t>
+  </si>
+  <si>
+    <t>exact</t>
+  </si>
+  <si>
+    <t>Global Aggregate Bonds</t>
+  </si>
+  <si>
+    <t>global_bonds</t>
+  </si>
+  <si>
+    <t>Broad emerging markets equity exposure.</t>
+  </si>
+  <si>
+    <t>Broad emerging markets equity</t>
+  </si>
+  <si>
+    <t>Emerging Markets Equity</t>
+  </si>
+  <si>
+    <t>em_equity</t>
+  </si>
+  <si>
+    <t>US large-cap equity exposure tracking the S&amp;P 500 or equivalent.</t>
+  </si>
+  <si>
+    <t>US large-cap equity</t>
+  </si>
+  <si>
+    <t>S&amp;P 500 Equity</t>
+  </si>
+  <si>
+    <t>sp500</t>
+  </si>
+  <si>
+    <t>Very similar to all-world/global ACWI-style exposure, but may track a different index family.</t>
+  </si>
+  <si>
+    <t>Global equity (all-country)</t>
+  </si>
+  <si>
+    <t>near</t>
+  </si>
+  <si>
+    <t>Broad Global Equity</t>
+  </si>
+  <si>
+    <t>global_equity_broad</t>
+  </si>
+  <si>
+    <t>Broad all-country global equity exposure including developed and emerging markets.</t>
+  </si>
+  <si>
+    <t>Global equity (developed + emerging)</t>
+  </si>
+  <si>
+    <t>Global All-World Equity</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>canonical_exposure</t>
+  </si>
+  <si>
+    <t>group_type</t>
+  </si>
+  <si>
+    <t>equivalence_group_name</t>
+  </si>
+  <si>
+    <t>Bond exposure serves a different role from emerging equity.</t>
+  </si>
+  <si>
+    <t>different_role</t>
+  </si>
+  <si>
+    <t>Bond exposure serves a different role from US large-cap equity.</t>
+  </si>
+  <si>
+    <t>Bond exposure serves a different role from broad equity.</t>
+  </si>
+  <si>
+    <t>Bond exposure serves a different role from global equity.</t>
+  </si>
+  <si>
+    <t>Equivalent broad global bond exposure.</t>
+  </si>
+  <si>
+    <t>Emerging markets are not a substitute for US large-cap exposure.</t>
+  </si>
+  <si>
+    <t>Emerging market ETF can complement or tilt broad global exposure.</t>
+  </si>
+  <si>
+    <t>complement</t>
+  </si>
+  <si>
+    <t>Emerging market ETF can complement or tilt global all-world exposure.</t>
+  </si>
+  <si>
+    <t>Equivalent broad emerging markets exposure.</t>
+  </si>
+  <si>
+    <t>Bond exposure serves a different role from US equity.</t>
+  </si>
+  <si>
+    <t>Emerging markets are not an equivalent US large-cap replacement.</t>
+  </si>
+  <si>
+    <t>S&amp;P 500 overlaps heavily with broad global equity.</t>
+  </si>
+  <si>
+    <t>overlap</t>
+  </si>
+  <si>
+    <t>S&amp;P 500 overlaps heavily with global all-world due to US weight.</t>
+  </si>
+  <si>
+    <t>Equivalent S&amp;P 500 exposure.</t>
+  </si>
+  <si>
+    <t>US large-cap equity is a major subset of broad global equity.</t>
+  </si>
+  <si>
+    <t>Very similar all-country global equity exposure.</t>
+  </si>
+  <si>
+    <t>Same broad global equity exposure group.</t>
+  </si>
+  <si>
+    <t>Emerging markets can complement or tilt a global portfolio.</t>
+  </si>
+  <si>
+    <t>US large-cap exposure is a major subset of global all-world exposure.</t>
+  </si>
+  <si>
+    <t>Very similar all-country global equity exposure, but not the same index family.</t>
+  </si>
+  <si>
+    <t>Same core exposure; different share classes/providers may live here later.</t>
+  </si>
+  <si>
+    <t>priority_rank</t>
+  </si>
+  <si>
+    <t>relationship_type</t>
+  </si>
+  <si>
+    <t>target_group_code</t>
+  </si>
+  <si>
+    <t>source_group_code</t>
+  </si>
+  <si>
+    <t>relationship_to_group</t>
   </si>
 </sst>
 </file>
@@ -274,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -286,10 +450,11 @@
     <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -319,16 +484,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tbl_etf_info" displayName="tbl_etf_info" ref="A1:S2">
-  <autoFilter ref="A1:S2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tbl_etf_info" displayName="tbl_etf_info" ref="A1:T2">
+  <autoFilter ref="A1:T2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="etf"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ticker"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="isin"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="fund_name"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="provider_key"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="index_key"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="equivalence_group_key"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="provider"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="index"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="equivalence_group_code"/>
+    <tableColumn id="20" xr3:uid="{AD47DD8B-545D-46E7-A8EC-D0DE1799A045}" name="relationship_to_group"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="asset_class"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="category"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="distribution_type"/>
@@ -337,7 +503,7 @@
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="domicile"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="hedged_flag"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="ucits_flag"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="ter" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="ter" dataDxfId="2"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="inception_date"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="is_active"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="notes"/>
@@ -352,7 +518,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="etf"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="geography"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="exposure_weight" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="exposure_weight" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -655,33 +821,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="41.28515625" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" customWidth="1"/>
-    <col min="7" max="7" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="49.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="41.33203125" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" customWidth="1"/>
+    <col min="7" max="7" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.109375" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="49.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>52</v>
+    <row r="1" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -692,109 +859,115 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="T1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="Q2" s="4">
+        <v>0.19</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="S2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P2" s="4">
-        <v>0.19</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -808,76 +981,76 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>54</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4">
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C3" s="4">
         <v>0.04</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C4" s="4">
         <v>0.26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C5" s="4">
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="8">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="5">
         <v>0</v>
       </c>
     </row>
@@ -893,153 +1066,153 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>53</v>
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C2" s="4">
         <v>0.29470000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C3" s="4">
         <v>0.1552</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C4" s="4">
         <v>0.13370000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C5" s="4">
         <v>0.1235</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C6" s="4">
         <v>8.5500000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C7" s="4">
         <v>4.5499999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C8" s="4">
         <v>4.2099999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4">
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C10" s="4">
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C11" s="4">
         <v>2.9899999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C12" s="4">
         <v>2.0299999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="8">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="5">
         <v>1E-4</v>
       </c>
     </row>
@@ -1049,4 +1222,581 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{120F4820-5F08-4C75-9AB9-C81B79B18B77}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
+    <col min="5" max="5" width="76.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A55DD90-EEA5-4896-AFFB-1B743F33A686}">
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="65.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>